--- a/data/file_generation/reference/data_212/AI_项目不同阶段收益估算_res.xlsx
+++ b/data/file_generation/reference/data_212/AI_项目不同阶段收益估算_res.xlsx
@@ -1544,18 +1544,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0502BC-4AC7-4FF6-BB95-5CE0DB58F535}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B00DCD-6AC9-488B-9E8F-F62EAAB2B58A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8309BFF2-351A-432A-A14F-99FB03CB8290}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05F682CC-7D04-4464-BEA1-7B0EF2142AFA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28087C92-D210-4762-ACC6-4899E37198C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3316BEE0-C0D2-4D39-A082-B9C746D2EFC9}"/>
 </file>